--- a/compliance/Oshinei_ERP_SoD_Matrix_v1.xlsx
+++ b/compliance/Oshinei_ERP_SoD_Matrix_v1.xlsx
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Permission Inventory'!$A$1:$F$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SoD Rules'!$A$1:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SoD Rules'!$A$1:$H$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Detected Conflicts'!$A$1:$H$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -762,7 +762,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>13 SoD conflict rules; a role conflicts when it holds duties on BOTH sides of a rule</t>
+          <t>16 SoD conflict rules; a role conflicts when it holds duties on BOTH sides of a rule</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2718,8 +2718,134 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Configure rewards / vouchers</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>POS redemption at till</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>crm_reward</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>pos_sell</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Create a reward/voucher and redeem it for oneself at the till.</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>Separate reward-catalog configuration from POS redemption; review reward-change + redemption reports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Manual points adjustment</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Member master maintenance</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>crm_points_adjust</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>crm_member</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Enrol a ghost member and credit points to it.</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Separate member enrolment from points adjustment; over-threshold adjust via maker-checker approval.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Campaign issuance of point-bearing value</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Points adjustment</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>crm_campaign</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>crm_points_adjust</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Self-issue loyalty value through two channels (campaign coupons + manual adjustment).</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>Separate campaign issuance from points adjustment; review issuance + adjustment logs.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H14"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3847,7 +3973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3864,7 +3990,10 @@
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="6" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -3940,6 +4069,21 @@
       </c>
       <c r="O1" s="21" t="inlineStr">
         <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="P1" s="21" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="Q1" s="21" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="R1" s="21" t="inlineStr">
+        <is>
           <t># Conflicts</t>
         </is>
       </c>
@@ -4015,7 +4159,22 @@
           <t>▲</t>
         </is>
       </c>
-      <c r="O2" s="24" t="inlineStr">
+      <c r="O2" s="23" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="P2" s="23" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="Q2" s="23" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="R2" s="24" t="inlineStr">
         <is>
           <t>ALL (▲)</t>
         </is>
@@ -4092,7 +4251,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O3" s="20" t="n">
+      <c r="O3" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P3" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q3" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R3" s="20" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4167,7 +4341,22 @@
           <t>✕</t>
         </is>
       </c>
-      <c r="O4" s="20" t="n">
+      <c r="O4" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P4" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q4" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R4" s="20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4242,7 +4431,22 @@
           <t>✕</t>
         </is>
       </c>
-      <c r="O5" s="20" t="n">
+      <c r="O5" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P5" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q5" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R5" s="20" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4317,7 +4521,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O6" s="20" t="n">
+      <c r="O6" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P6" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q6" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R6" s="20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4392,7 +4611,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O7" s="20" t="n">
+      <c r="O7" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P7" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q7" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R7" s="20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5273,7 +5507,7 @@
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Holds every duty — inherently violates all 13 rules by design.</t>
+          <t>Holds every duty — inherently violates all 16 rules by design.</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -5871,7 +6105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5888,7 +6122,10 @@
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="6" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5971,6 +6208,21 @@
       </c>
       <c r="O2" s="21" t="inlineStr">
         <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="P2" s="21" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="Q2" s="21" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="R2" s="21" t="inlineStr">
+        <is>
           <t># Conflicts</t>
         </is>
       </c>
@@ -6046,7 +6298,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O3" s="37" t="n">
+      <c r="O3" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P3" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q3" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R3" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6121,7 +6388,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O4" s="37" t="n">
+      <c r="O4" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P4" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q4" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R4" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6196,7 +6478,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O5" s="37" t="n">
+      <c r="O5" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P5" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q5" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R5" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6271,7 +6568,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O6" s="37" t="n">
+      <c r="O6" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P6" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q6" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R6" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6346,7 +6658,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O7" s="37" t="n">
+      <c r="O7" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P7" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q7" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R7" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6421,7 +6748,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O8" s="37" t="n">
+      <c r="O8" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P8" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q8" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R8" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6496,7 +6838,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O9" s="37" t="n">
+      <c r="O9" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P9" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q9" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R9" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6571,7 +6928,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O10" s="37" t="n">
+      <c r="O10" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P10" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q10" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R10" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6646,7 +7018,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O11" s="37" t="n">
+      <c r="O11" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P11" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q11" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R11" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6721,7 +7108,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O12" s="37" t="n">
+      <c r="O12" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P12" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q12" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R12" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6796,7 +7198,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O13" s="37" t="n">
+      <c r="O13" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P13" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q13" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R13" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6871,7 +7288,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O14" s="37" t="n">
+      <c r="O14" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P14" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q14" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R14" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6946,7 +7378,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O15" s="37" t="n">
+      <c r="O15" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P15" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q15" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R15" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7021,7 +7468,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O16" s="37" t="n">
+      <c r="O16" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P16" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q16" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R16" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7096,7 +7558,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O17" s="37" t="n">
+      <c r="O17" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P17" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q17" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R17" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7171,7 +7648,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O18" s="37" t="n">
+      <c r="O18" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P18" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q18" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R18" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7246,7 +7738,22 @@
           <t>·</t>
         </is>
       </c>
-      <c r="O19" s="37" t="n">
+      <c r="O19" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P19" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q19" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R19" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7321,7 +7828,22 @@
           <t>▲</t>
         </is>
       </c>
-      <c r="O20" s="24" t="inlineStr">
+      <c r="O20" s="23" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="P20" s="23" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="Q20" s="23" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="R20" s="24" t="inlineStr">
         <is>
           <t>ALL (▲)</t>
         </is>
@@ -7339,7 +7861,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A22:O24"/>
+    <mergeCell ref="A22:R24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/compliance/Oshinei_ERP_SoD_Matrix_v1.xlsx
+++ b/compliance/Oshinei_ERP_SoD_Matrix_v1.xlsx
@@ -18,9 +18,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remediated Matrix" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Permission Inventory'!$A$1:$F$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Permission Inventory'!$A$1:$F$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SoD Rules'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Detected Conflicts'!$A$1:$H$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Detected Conflicts'!$A$1:$H$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -774,7 +774,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22  ·  Version 1.0 — review with auditor + SOX advisor</t>
+          <t>2026-06-22  ·  Version 1.1 — Planner remediated 2026-06-26 (was 14 conflicts, now 8)</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Admin, Planner, Warehouse</t>
+          <t>Admin, Warehouse</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Raise purchase requisitions / POs</t>
+          <t>Create &amp; approve purchase orders (buying)</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -1148,39 +1148,39 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>creditors</t>
+          <t>pr_raise</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Finance &amp; AR/AP</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Accounts payable: pay vendors, match tolerance</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Raise a purchase requisition (company-wide; PR is a request, not a commitment)</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Admin, Procurement</t>
+          <t>Admin, Sales, Procurement, Planner, Warehouse</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>payments; match.controller; ledger</t>
+          <t>procurement.controller /requisitions</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>creditors</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Accounts receivable; AR/JE posting</t>
+          <t>Accounts payable: pay vendors, match tolerance</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -1200,51 +1200,51 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Admin, Sales, Procurement</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>ledger.controller; finance</t>
+          <t>payments; match.controller; ledger</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>delivery</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Sales &amp; Orders</t>
+          <t>Finance &amp; AR/AP</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Delivery dispatch</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Accounts receivable; AR/JE posting</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Admin, Sales, Procurement</t>
+          <t>Admin, Sales</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>delivery</t>
+          <t>ledger.controller; finance</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>returns</t>
+          <t>delivery</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
@@ -1254,29 +1254,29 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Process customer returns</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Delivery dispatch</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Admin, Sales</t>
+          <t>Admin, Sales, Procurement</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>returns.controller</t>
+          <t>delivery</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>pricelist</t>
+          <t>returns</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Maintain price lists</t>
+          <t>Process customer returns</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
@@ -1301,46 +1301,46 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>pricing</t>
+          <t>returns.controller</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>lots</t>
+          <t>pricelist</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Sales &amp; Orders</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Lot/batch management</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Maintain price lists</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Admin, Warehouse</t>
+          <t>Admin, Sales</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>lots</t>
+          <t>pricing</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>locations</t>
+          <t>lots</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Location/bin management</t>
+          <t>Lot/batch management</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
@@ -1360,83 +1360,83 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Admin, Warehouse</t>
+          <t>Admin, Planner, Warehouse</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>wms locations</t>
+          <t>lots</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>promos</t>
+          <t>locations</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Sales &amp; Orders</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Maintain promotions/discounts</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Location/bin management</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Admin, Sales</t>
+          <t>Admin, Planner, Warehouse</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>marketing/promos</t>
+          <t>wms locations</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>mobile</t>
+          <t>promos</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Sales &amp; Orders</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Mobile scanning</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Maintain promotions/discounts</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Admin, Warehouse</t>
+          <t>Admin, Sales</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>scan; mobile-scan</t>
+          <t>marketing/promos</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Item images</t>
+          <t>Mobile scanning</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
@@ -1461,46 +1461,46 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>scan; mobile-scan</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>masterdata</t>
+          <t>images</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Master data: vendor/item/config maintenance</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Item images</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Admin, Procurement, Planner, Warehouse</t>
+          <t>Admin, Warehouse</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>masterdata; admin-config</t>
+          <t>images</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>bom_master</t>
+          <t>masterdata</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
@@ -1510,39 +1510,39 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>BOM master maintenance</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Master data: vendor/item/config maintenance</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Admin, Warehouse</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>bom; mfg</t>
+          <t>masterdata; admin-config</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>planner</t>
+          <t>bom_master</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Dashboard &amp; Analytics</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Planning / forecasting</t>
+          <t>BOM master maintenance</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
@@ -1552,19 +1552,19 @@
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Admin, Sales, Planner</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>planning</t>
+          <t>bom; mfg</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>exec</t>
+          <t>planner</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Executive/finance: GL postings, period &amp; year-end close, recon prep</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Planning / forecasting</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
@@ -1589,46 +1589,46 @@
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>ledger.controller; reconciliation.controller</t>
+          <t>planning</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>order_cust</t>
+          <t>exec</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Customer Portal</t>
+          <t>Dashboard &amp; Analytics</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Customer self-order</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Executive/finance: GL postings, period &amp; year-end close, recon prep</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Admin, Customer</t>
+          <t>Admin, Sales</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>portal order</t>
+          <t>ledger.controller; reconciliation.controller</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>cust_dash</t>
+          <t>order_cust</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Customer dashboard</t>
+          <t>Customer self-order</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
@@ -1653,14 +1653,14 @@
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>portal dashboard</t>
+          <t>portal order</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>cust_inventory</t>
+          <t>cust_dash</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Customer inventory view</t>
+          <t>Customer dashboard</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
@@ -1685,14 +1685,14 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>portal inventory</t>
+          <t>portal dashboard</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>cust_pos</t>
+          <t>cust_inventory</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Customer self-checkout (portal POS)</t>
+          <t>Customer inventory view</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
@@ -1717,14 +1717,14 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>portal/pos</t>
+          <t>portal inventory</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>cust_bom</t>
+          <t>cust_pos</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Customer BOM view</t>
+          <t>Customer self-checkout (portal POS)</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
@@ -1749,14 +1749,14 @@
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>portal bom</t>
+          <t>portal/pos</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>cust_variance</t>
+          <t>cust_bom</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Customer variance view</t>
+          <t>Customer BOM view</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
@@ -1781,14 +1781,14 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>portal variance</t>
+          <t>portal bom</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>loyalty</t>
+          <t>cust_variance</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Loyalty points (own)</t>
+          <t>Customer variance view</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
@@ -1813,14 +1813,14 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>loyalty</t>
+          <t>portal variance</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>loyalty</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Surveys</t>
+          <t>Loyalty points (own)</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
@@ -1845,24 +1845,24 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>loyalty</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>cust_my_crm</t>
+          <t>survey</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>My Business</t>
+          <t>Customer Portal</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Own-org CRM</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -1877,14 +1877,14 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>portal/my</t>
+          <t>survey</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>cust_my_suppliers</t>
+          <t>cust_my_crm</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Own-org suppliers</t>
+          <t>Own-org CRM</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
@@ -1916,7 +1916,7 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>cust_my_pos</t>
+          <t>cust_my_suppliers</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Own-org purchase orders</t>
+          <t>Own-org suppliers</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
@@ -1948,7 +1948,7 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>cust_my_users</t>
+          <t>cust_my_pos</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Own-org user management</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Own-org purchase orders</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
@@ -1973,56 +1973,56 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>portal/my/users</t>
+          <t>portal/my</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>cust_my_users</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Dashboard &amp; Analytics</t>
+          <t>My Business</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Marketing campaigns</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Own-org user management</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Admin, Sales</t>
+          <t>Admin, Customer</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>portal/my/users</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>track</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Customer Portal</t>
+          <t>Dashboard &amp; Analytics</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Order tracking</t>
+          <t>Marketing campaigns</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
@@ -2032,29 +2032,29 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Admin, Customer</t>
+          <t>Admin, Sales</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>track</t>
+          <t>marketing</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>ai_chat</t>
+          <t>track</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Customer Portal</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>AI assistant</t>
+          <t>Order tracking</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
@@ -2064,49 +2064,81 @@
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Admin, Customer</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>track</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
+          <t>ai_chat</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>AI assistant</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
           <t>approvals</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>Administration</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>Approve workflow items; certify reconciliation; run consolidation</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>Admin, Sales, Procurement, Planner</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>Admin, Sales</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
         <is>
           <t>workflow; reconciliation certify; consolidation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F39"/>
+  <autoFilter ref="A1:F40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2856,7 +2888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3085,11 +3117,7 @@
       </c>
       <c r="D8" s="17" t="inlineStr"/>
       <c r="E8" s="17" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
+      <c r="F8" s="17" t="inlineStr"/>
       <c r="G8" s="16" t="inlineStr">
         <is>
           <t>✕</t>
@@ -3130,12 +3158,12 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>creditors</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>pr_raise</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -3143,20 +3171,32 @@
           <t>✕</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr"/>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr"/>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
       <c r="H10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>creditors</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -3169,16 +3209,8 @@
           <t>✕</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
       <c r="F11" s="18" t="inlineStr"/>
       <c r="G11" s="18" t="inlineStr"/>
       <c r="H11" s="18" t="inlineStr"/>
@@ -3186,12 +3218,12 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>delivery</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -3204,11 +3236,7 @@
           <t>✕</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
+      <c r="E12" s="17" t="inlineStr"/>
       <c r="F12" s="17" t="inlineStr"/>
       <c r="G12" s="17" t="inlineStr"/>
       <c r="H12" s="17" t="inlineStr"/>
@@ -3216,12 +3244,12 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>returns</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>delivery</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -3234,7 +3262,11 @@
           <t>✕</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr"/>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
       <c r="F13" s="18" t="inlineStr"/>
       <c r="G13" s="18" t="inlineStr"/>
       <c r="H13" s="18" t="inlineStr"/>
@@ -3242,7 +3274,7 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>pricelist</t>
+          <t>returns</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -3268,12 +3300,12 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>lots</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>pricelist</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -3281,20 +3313,20 @@
           <t>✕</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr"/>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
       <c r="E15" s="18" t="inlineStr"/>
       <c r="F15" s="18" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
+      <c r="G15" s="18" t="inlineStr"/>
       <c r="H15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>locations</t>
+          <t>lots</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -3309,7 +3341,11 @@
       </c>
       <c r="D16" s="17" t="inlineStr"/>
       <c r="E16" s="17" t="inlineStr"/>
-      <c r="F16" s="17" t="inlineStr"/>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
           <t>✕</t>
@@ -3320,12 +3356,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>promos</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>locations</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -3333,25 +3369,29 @@
           <t>✕</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
+      <c r="D17" s="18" t="inlineStr"/>
       <c r="E17" s="18" t="inlineStr"/>
-      <c r="F17" s="18" t="inlineStr"/>
-      <c r="G17" s="18" t="inlineStr"/>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
       <c r="H17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>mobile</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>promos</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -3359,20 +3399,20 @@
           <t>✕</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr"/>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
       <c r="E18" s="17" t="inlineStr"/>
       <c r="F18" s="17" t="inlineStr"/>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
+      <c r="G18" s="17" t="inlineStr"/>
       <c r="H18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
@@ -3398,12 +3438,12 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>masterdata</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>images</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -3412,16 +3452,8 @@
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr"/>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
+      <c r="E20" s="17" t="inlineStr"/>
+      <c r="F20" s="17" t="inlineStr"/>
       <c r="G20" s="16" t="inlineStr">
         <is>
           <t>✕</t>
@@ -3432,12 +3464,12 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>bom_master</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>masterdata</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
@@ -3448,13 +3480,17 @@
       <c r="D21" s="18" t="inlineStr"/>
       <c r="E21" s="18" t="inlineStr"/>
       <c r="F21" s="18" t="inlineStr"/>
-      <c r="G21" s="18" t="inlineStr"/>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
       <c r="H21" s="18" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>planner</t>
+          <t>bom_master</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
@@ -3467,29 +3503,21 @@
           <t>✕</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
+      <c r="D22" s="17" t="inlineStr"/>
       <c r="E22" s="17" t="inlineStr"/>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
+      <c r="F22" s="17" t="inlineStr"/>
       <c r="G22" s="17" t="inlineStr"/>
       <c r="H22" s="17" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>exec</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>planner</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -3514,12 +3542,12 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>order_cust</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>exec</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -3527,20 +3555,20 @@
           <t>✕</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr"/>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
       <c r="E24" s="17" t="inlineStr"/>
       <c r="F24" s="17" t="inlineStr"/>
       <c r="G24" s="17" t="inlineStr"/>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
+      <c r="H24" s="17" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>cust_dash</t>
+          <t>order_cust</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -3566,7 +3594,7 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>cust_inventory</t>
+          <t>cust_dash</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
@@ -3592,7 +3620,7 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>cust_pos</t>
+          <t>cust_inventory</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
@@ -3618,7 +3646,7 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>cust_bom</t>
+          <t>cust_pos</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
@@ -3644,7 +3672,7 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>cust_variance</t>
+          <t>cust_bom</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
@@ -3670,7 +3698,7 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>loyalty</t>
+          <t>cust_variance</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
@@ -3696,7 +3724,7 @@
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>loyalty</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
@@ -3722,7 +3750,7 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>cust_my_crm</t>
+          <t>survey</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
@@ -3748,7 +3776,7 @@
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>cust_my_suppliers</t>
+          <t>cust_my_crm</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
@@ -3774,7 +3802,7 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>cust_my_pos</t>
+          <t>cust_my_suppliers</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
@@ -3800,12 +3828,12 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>cust_my_users</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>cust_my_pos</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
@@ -3826,12 +3854,12 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>marketing</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>cust_my_users</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
@@ -3839,20 +3867,20 @@
           <t>✕</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
+      <c r="D36" s="17" t="inlineStr"/>
       <c r="E36" s="17" t="inlineStr"/>
       <c r="F36" s="17" t="inlineStr"/>
       <c r="G36" s="17" t="inlineStr"/>
-      <c r="H36" s="17" t="inlineStr"/>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>track</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
@@ -3865,20 +3893,20 @@
           <t>✕</t>
         </is>
       </c>
-      <c r="D37" s="18" t="inlineStr"/>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
       <c r="E37" s="18" t="inlineStr"/>
       <c r="F37" s="18" t="inlineStr"/>
       <c r="G37" s="18" t="inlineStr"/>
-      <c r="H37" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
+      <c r="H37" s="18" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>ai_chat</t>
+          <t>track</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
@@ -3895,17 +3923,21 @@
       <c r="E38" s="17" t="inlineStr"/>
       <c r="F38" s="17" t="inlineStr"/>
       <c r="G38" s="17" t="inlineStr"/>
-      <c r="H38" s="17" t="inlineStr"/>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>approvals</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>ai_chat</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="C39" s="16" t="inlineStr">
@@ -3913,52 +3945,66 @@
           <t>✕</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
+      <c r="D39" s="18" t="inlineStr"/>
+      <c r="E39" s="18" t="inlineStr"/>
+      <c r="F39" s="18" t="inlineStr"/>
       <c r="G39" s="18" t="inlineStr"/>
       <c r="H39" s="18" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="19" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>approvals</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr"/>
+      <c r="F40" s="17" t="inlineStr"/>
+      <c r="G40" s="17" t="inlineStr"/>
+      <c r="H40" s="17" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C40" s="20">
-        <f>COUNTIF(C2:C39,"✕")</f>
+      <c r="C41" s="20">
+        <f>COUNTIF(C2:C40,"✕")</f>
         <v/>
       </c>
-      <c r="D40" s="20">
-        <f>COUNTIF(D2:D39,"✕")</f>
+      <c r="D41" s="20">
+        <f>COUNTIF(D2:D40,"✕")</f>
         <v/>
       </c>
-      <c r="E40" s="20">
-        <f>COUNTIF(E2:E39,"✕")</f>
+      <c r="E41" s="20">
+        <f>COUNTIF(E2:E40,"✕")</f>
         <v/>
       </c>
-      <c r="F40" s="20">
-        <f>COUNTIF(F2:F39,"✕")</f>
+      <c r="F41" s="20">
+        <f>COUNTIF(F2:F40,"✕")</f>
         <v/>
       </c>
-      <c r="G40" s="20">
-        <f>COUNTIF(G2:G39,"✕")</f>
+      <c r="G41" s="20">
+        <f>COUNTIF(G2:G40,"✕")</f>
         <v/>
       </c>
-      <c r="H40" s="20">
-        <f>COUNTIF(H2:H39,"✕")</f>
+      <c r="H41" s="20">
+        <f>COUNTIF(H2:H40,"✕")</f>
         <v/>
       </c>
     </row>
@@ -4281,14 +4327,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="inlineStr">
-        <is>
-          <t>✕</t>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
         </is>
       </c>
       <c r="E4" s="25" t="inlineStr">
@@ -4306,9 +4352,9 @@
           <t>·</t>
         </is>
       </c>
-      <c r="H4" s="26" t="inlineStr">
-        <is>
-          <t>✕</t>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
         </is>
       </c>
       <c r="I4" s="25" t="inlineStr">
@@ -4336,9 +4382,9 @@
           <t>·</t>
         </is>
       </c>
-      <c r="N4" s="26" t="inlineStr">
-        <is>
-          <t>✕</t>
+      <c r="N4" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
         </is>
       </c>
       <c r="O4" s="25" t="inlineStr">
@@ -4357,7 +4403,7 @@
         </is>
       </c>
       <c r="R4" s="20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4381,24 +4427,24 @@
           <t>·</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="F5" s="26" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="G5" s="26" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="H5" s="26" t="inlineStr">
-        <is>
-          <t>✕</t>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
         </is>
       </c>
       <c r="I5" s="25" t="inlineStr">
@@ -4416,9 +4462,9 @@
           <t>·</t>
         </is>
       </c>
-      <c r="L5" s="26" t="inlineStr">
-        <is>
-          <t>✕</t>
+      <c r="L5" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
         </is>
       </c>
       <c r="M5" s="25" t="inlineStr">
@@ -4426,9 +4472,9 @@
           <t>·</t>
         </is>
       </c>
-      <c r="N5" s="26" t="inlineStr">
-        <is>
-          <t>✕</t>
+      <c r="N5" s="25" t="inlineStr">
+        <is>
+          <t>·</t>
         </is>
       </c>
       <c r="O5" s="25" t="inlineStr">
@@ -4447,7 +4493,7 @@
         </is>
       </c>
       <c r="R5" s="20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4668,7 +4714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4726,32 +4772,32 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Planner</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
-          <t>R04</t>
+          <t>R05</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Purchase ordering</t>
+          <t>Post journal entries</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Goods receipt / warehouse custody</t>
+          <t>Close fiscal period / year</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>procurement, warehouse</t>
+          <t>ar, exec</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>Order goods and confirm receipt — defeats 3-way match (phantom receipts).</t>
+          <t>Post entries and also close the period — conceal misstatement after the fact.</t>
         </is>
       </c>
       <c r="G2" s="10" t="inlineStr">
@@ -4761,123 +4807,123 @@
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>Separate procurement from receiving; independent GR; rely on 3-way match (EXP-01).</t>
+          <t>Restrict period/year close to a finance approver distinct from JE preparers; JE maker-checker (GL-05).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Planner</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>R05</t>
+          <t>R06</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Post journal entries</t>
+          <t>Prepare reconciliation</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Close fiscal period / year</t>
+          <t>Certify reconciliation</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>exec</t>
+          <t>approvals, exec</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>Post entries and also close the period — conceal misstatement after the fact.</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Prepare and self-certify a reconciliation — no independent review.</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Restrict period/year close to a finance approver distinct from JE preparers; JE maker-checker (GL-05).</t>
+          <t>Preparer must differ from certifier; certification by an independent approver.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>Planner</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B4" s="31" t="inlineStr">
         <is>
-          <t>R06</t>
+          <t>R07</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Prepare reconciliation</t>
+          <t>Initiate transactions</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Certify reconciliation</t>
+          <t>Approve workflow items</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>approvals, exec</t>
+          <t>approvals, ar, order_mgt, pos</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Prepare and self-certify a reconciliation — no independent review.</t>
-        </is>
-      </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Initiate a transaction and approve it in the workflow — self-approval.</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>Preparer must differ from certifier; certification by an independent approver.</t>
+          <t>Approver must differ from initiator; enforce in the approval engine.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Planner</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B5" s="32" t="inlineStr">
         <is>
-          <t>R07</t>
+          <t>R08</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Initiate transactions</t>
+          <t>Record sale</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Approve workflow items</t>
+          <t>Issue refund / reconcile till (within 'pos')</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>approvals, procurement</t>
+          <t>pos</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Initiate a transaction and approve it in the workflow — self-approval.</t>
+          <t>The 'pos' permission BUNDLES sell + refund/void + till close — one cashier can ring, refund and reconcile their own drawer.</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -4887,39 +4933,39 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Approver must differ from initiator; enforce in the approval engine.</t>
+          <t>Split 'pos' into sub-permissions (sell vs refund/void vs till close); require manager auth for refund/void; independent till count.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Planner</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R09</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Adjust inventory</t>
+          <t>Maintain customer / credit master</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Stock custody &amp; counting (within 'warehouse')</t>
+          <t>Enter sales orders</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>crm, order_mgt, pos</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>'warehouse' bundles adjust + custody + count — conceal shrink/theft via adjustments.</t>
+          <t>Raise a customer's credit limit and then sell on credit to them — bad-debt / collusion risk.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -4929,39 +4975,39 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Separate adjustment authority from physical count; independent count + variance approval (INV-04).</t>
+          <t>Separate customer/credit-limit maintenance from order entry; credit-change report reviewed.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Planner</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Maintain master data / config</t>
+          <t>Maintain prices / promotions</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Transact on it</t>
+          <t>Enter sales</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>masterdata, procurement</t>
+          <t>order_mgt, pos, pricelist, promos</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Change configuration/master data and transact against it without review.</t>
+          <t>Set a price/discount and sell at it — under-pricing/collusion.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -4971,558 +5017,138 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Segregate config from operations; master-data change log reviewed independently.</t>
+          <t>Separate price/promo maintenance from selling; price-override report reviewed.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Maintain vendor/master data</t>
+          <t>Process returns</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Disburse AP / pay vendors</t>
+          <t>Issue refund</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>creditors, masterdata</t>
+          <t>ar, pos, returns</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Create a fictitious/edited vendor and pay it — classic disbursement fraud.</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Process a return and issue the matching refund unchecked.</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>Separate vendor-master maintenance from AP payment; vendor-change report reviewed independently.</t>
+          <t>Independent approval of refunds on returns; over-return guard (REV-07) + detective review.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>R03</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Raise purchase requisition / PO</t>
+          <t>Adjust inventory</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Approve &amp; pay AP</t>
+          <t>Stock custody &amp; counting (within 'warehouse')</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>creditors, procurement</t>
+          <t>locations, lots, warehouse</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Originate a purchase and also pay it — unauthorized/duplicate spend.</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
+          <t>'warehouse' bundles adjust + custody + count — conceal shrink/theft via adjustments.</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>Separate adjustment authority from physical count; independent count + variance approval (INV-04).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="inlineStr">
+        <is>
+          <t>(superuser)</t>
+        </is>
+      </c>
+      <c r="D10" s="34" t="inlineStr">
+        <is>
+          <t>(superuser)</t>
+        </is>
+      </c>
+      <c r="E10" s="34" t="inlineStr">
+        <is>
+          <t>ALL 38 permissions</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Holds every duty — inherently violates all 16 rules by design.</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>Split buying from paying; route PO/payment through maker-checker approvals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Procurement</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="inlineStr">
-        <is>
-          <t>R07</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Initiate transactions</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Approve workflow items</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>approvals, ar, creditors, procurement</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>Initiate a transaction and approve it in the workflow — self-approval.</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>Approver must differ from initiator; enforce in the approval engine.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Procurement</t>
-        </is>
-      </c>
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>R13</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Maintain master data / config</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Transact on it</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>ar, creditors, masterdata, procurement</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Change configuration/master data and transact against it without review.</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>Segregate config from operations; master-data change log reviewed independently.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="B12" s="31" t="inlineStr">
-        <is>
-          <t>R05</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Post journal entries</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Close fiscal period / year</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>ar, exec</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>Post entries and also close the period — conceal misstatement after the fact.</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>Restrict period/year close to a finance approver distinct from JE preparers; JE maker-checker (GL-05).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="B13" s="32" t="inlineStr">
-        <is>
-          <t>R06</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Prepare reconciliation</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Certify reconciliation</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>approvals, exec</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Prepare and self-certify a reconciliation — no independent review.</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>Preparer must differ from certifier; certification by an independent approver.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="B14" s="31" t="inlineStr">
-        <is>
-          <t>R07</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Initiate transactions</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Approve workflow items</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>approvals, ar, order_mgt, pos</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>Initiate a transaction and approve it in the workflow — self-approval.</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>Approver must differ from initiator; enforce in the approval engine.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="B15" s="32" t="inlineStr">
-        <is>
-          <t>R08</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Record sale</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Issue refund / reconcile till (within 'pos')</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>pos</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>The 'pos' permission BUNDLES sell + refund/void + till close — one cashier can ring, refund and reconcile their own drawer.</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>Split 'pos' into sub-permissions (sell vs refund/void vs till close); require manager auth for refund/void; independent till count.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>R09</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Maintain customer / credit master</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Enter sales orders</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>crm, order_mgt, pos</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>Raise a customer's credit limit and then sell on credit to them — bad-debt / collusion risk.</t>
-        </is>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>Separate customer/credit-limit maintenance from order entry; credit-change report reviewed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="B17" s="32" t="inlineStr">
-        <is>
-          <t>R10</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>Maintain prices / promotions</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Enter sales</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>order_mgt, pos, pricelist, promos</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>Set a price/discount and sell at it — under-pricing/collusion.</t>
-        </is>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>Separate price/promo maintenance from selling; price-override report reviewed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Process returns</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Issue refund</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>ar, pos, returns</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>Process a return and issue the matching refund unchecked.</t>
-        </is>
-      </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>Independent approval of refunds on returns; over-return guard (REV-07) + detective review.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
-      <c r="B19" s="32" t="inlineStr">
-        <is>
-          <t>R11</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>Adjust inventory</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Stock custody &amp; counting (within 'warehouse')</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>locations, lots, warehouse</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>'warehouse' bundles adjust + custody + count — conceal shrink/theft via adjustments.</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>Separate adjustment authority from physical count; independent count + variance approval (INV-04).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="B20" s="33" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="C20" s="34" t="inlineStr">
-        <is>
-          <t>(superuser)</t>
-        </is>
-      </c>
-      <c r="D20" s="34" t="inlineStr">
-        <is>
-          <t>(superuser)</t>
-        </is>
-      </c>
-      <c r="E20" s="34" t="inlineStr">
-        <is>
-          <t>ALL 38 permissions</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>Holds every duty — inherently violates all 16 rules by design.</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>Minimize named Admins; MFA (ITGC-AC-06); break-glass procedure; full reliance on audit log + hash-chained journal (ITGC-AC-10/11) + periodic privileged-access review.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H20"/>
+  <autoFilter ref="A1:H10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7852,7 +7478,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Result: 0 residual conflicts across the 17 operational roles (target 0). 'Superuser/Admin' remains an inherent superuser (break-glass) — mitigated by minimal named users, MFA, and the tamper-evident audit log + hash-chained journal. Compare with the 'Conflict Matrix' tab (current design: 18 conflicts).</t>
+          <t>Result: 0 residual conflicts across the 17 operational roles (target 0). 'Superuser/Admin' remains an inherent superuser (break-glass) — mitigated by minimal named users, MFA, and the tamper-evident audit log + hash-chained journal. Compare with the 'Conflict Matrix' tab (current design: 8 conflicts — Procurement remediated 2026-06-26 from 18→14; Planner then remediated 2026-06-26 from 14→8).</t>
         </is>
       </c>
     </row>
